--- a/HSI_FSC_result/5. KshotNquery/score_support10_test10.xlsx
+++ b/HSI_FSC_result/5. KshotNquery/score_support10_test10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_5_support10_test10\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\5. KshotNquery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818F7FFB-B109-444B-9F22-2B382E1CEC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A699A8DF-4E93-46AF-906F-E99F0BF84FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11985" yWindow="1470" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -79,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -358,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>19.565218000000002</v>
       </c>
@@ -396,7 +403,7 @@
         <v>27.857264199999996</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>52.673797999999998</v>
       </c>
@@ -432,7 +439,7 @@
         <v>48.006890200000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>38.138686999999997</v>
       </c>
@@ -468,7 +475,7 @@
         <v>35.081205300000008</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>47.272728000000001</v>
       </c>
@@ -504,7 +511,7 @@
         <v>33.265721900000003</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>31.428571999999999</v>
       </c>
@@ -540,7 +547,7 @@
         <v>56.608689300000002</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>57.162726999999997</v>
       </c>
@@ -576,7 +583,7 @@
         <v>81.129217199999999</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>18.421053000000001</v>
       </c>
@@ -612,7 +619,7 @@
         <v>27.6006213</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>51.710259999999998</v>
       </c>
@@ -648,7 +655,7 @@
         <v>77.424514700000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>17.241378999999998</v>
       </c>
@@ -684,7 +691,7 @@
         <v>17.215448700000003</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>35.309443999999999</v>
       </c>
@@ -720,7 +727,7 @@
         <v>35.953190799999994</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>56.709003000000003</v>
       </c>
@@ -756,7 +763,7 @@
         <v>63.207757100000002</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>39.249639999999999</v>
       </c>
@@ -792,7 +799,7 @@
         <v>38.534239099999994</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>72.363640000000004</v>
       </c>
@@ -828,7 +835,7 @@
         <v>61.593460800000003</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>76.525819999999996</v>
       </c>
@@ -864,7 +871,7 @@
         <v>84.895442400000007</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>50</v>
       </c>
@@ -900,7 +907,7 @@
         <v>43.986569099999997</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>70.454543999999999</v>
       </c>
@@ -936,7 +943,7 @@
         <v>69.282612100000009</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>46.863108595960497</v>
       </c>
@@ -972,7 +979,7 @@
         <v>50.232217777344069</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>45.889157056808401</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>50.102676451206143</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>40.897776685489397</v>
       </c>
@@ -1045,6 +1052,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1053,9 +1061,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>56.913918000000002</v>
       </c>
@@ -1091,7 +1099,7 @@
         <v>80.482924699999998</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>72.979020000000006</v>
       </c>
@@ -1127,7 +1135,7 @@
         <v>84.955755500000009</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>91.535150000000002</v>
       </c>
@@ -1163,7 +1171,7 @@
         <v>87.195953500000002</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>91.38158</v>
       </c>
@@ -1199,7 +1207,7 @@
         <v>88.037829400000007</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>95.522964000000002</v>
       </c>
@@ -1235,7 +1243,7 @@
         <v>95.275907000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>99.564769999999996</v>
       </c>
@@ -1271,7 +1279,7 @@
         <v>95.943688500000007</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>95.095129999999997</v>
       </c>
@@ -1307,7 +1315,7 @@
         <v>94.157138500000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>80.372370000000004</v>
       </c>
@@ -1343,7 +1351,7 @@
         <v>89.701656200000016</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>99.016760000000005</v>
       </c>
@@ -1379,7 +1387,7 @@
         <v>99.432183200000011</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>94.059110000000004</v>
       </c>
@@ -1415,7 +1423,7 @@
         <v>91.259105899999994</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>92.245990000000006</v>
       </c>
@@ -1451,7 +1459,7 @@
         <v>90.894076500000011</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>98.751360000000005</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>90.926309099999997</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>95.320999999999998</v>
       </c>
@@ -1523,7 +1531,7 @@
         <v>92.104346100000001</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>99.518299999999996</v>
       </c>
@@ -1559,7 +1567,7 @@
         <v>83.814750300000014</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>63.319670000000002</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>65.940477799999996</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>79.460920000000002</v>
       </c>
@@ -1631,7 +1639,7 @@
         <v>72.604071000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>84.551719041548793</v>
       </c>
@@ -1667,7 +1675,7 @@
         <v>85.262798130392156</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>87.816131114959703</v>
       </c>
@@ -1703,7 +1711,7 @@
         <v>87.670387625694218</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>82.832256739421098</v>
       </c>
@@ -1740,6 +1748,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1748,9 +1757,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>92.950450000000004</v>
       </c>
@@ -1786,7 +1795,7 @@
         <v>88.601094500000016</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>92.518929999999997</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>92.158845999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>72.517439999999993</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>60.745770199999995</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>81.979230000000001</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>73.452101600000006</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>88.896230000000003</v>
       </c>
@@ -1930,7 +1939,7 @@
         <v>89.753971000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>47.4559</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>44.1681253</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>38.287154999999998</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>42.825174699999991</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>77.762709999999998</v>
       </c>
@@ -2038,7 +2047,7 @@
         <v>77.338208100000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>70.470470000000006</v>
       </c>
@@ -2074,7 +2083,7 @@
         <v>76.976665399999987</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>77.971292313446796</v>
       </c>
@@ -2110,7 +2119,7 @@
         <v>72.273938657190911</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>73.648720979690495</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>71.779994368553133</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>71.684410847153899</v>
       </c>
@@ -2183,6 +2192,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2190,8 +2200,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2199,8 +2210,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>